--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260706.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260706.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>805,897</t>
+          <t>1,826,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,826,000</t>
+          <t>805,897</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,192,441</t>
+          <t>374,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>374,000</t>
+          <t>5,699,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>5,699,000</t>
+          <t>1,192,441</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>933,659</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>933,659</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>801,000</t>
+          <t>4,940,956</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,940,956</t>
+          <t>1,180,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,180,076</t>
+          <t>801,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>388,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,554,400</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>388,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>1,554,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,751,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>1,751,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>677,000</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>677,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
